--- a/output.xlsx
+++ b/output.xlsx
@@ -583,15 +583,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="136.38" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col hidden="1" width="13" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
@@ -604,9 +604,8 @@
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -634,7 +633,6 @@
       <c r="R1" s="3" t="n"/>
       <c r="S1" s="3" t="n"/>
       <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -661,7 +659,6 @@
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
-      <c r="U2" s="3" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="3" t="n"/>
@@ -684,7 +681,6 @@
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
-      <c r="U3" s="3" t="n"/>
     </row>
     <row r="4" ht="77" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -709,86 +705,81 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Вероятность реализации проекта</t>
+          <t>otrasl_ord</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>otrasl_ord</t>
+          <t>2024 год</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>2024 год</t>
+          <t>2025 год</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>2025 год</t>
+          <t>2026 год</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>2026 год</t>
+          <t>2027 год</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>2027 год</t>
+          <t>2028 год</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>2028 год</t>
+          <t>2029 год</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>2029 год</t>
+          <t>2030 год</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>2030 год</t>
+          <t>2031 год</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>2031 год</t>
+          <t>2032 год</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>2032 год</t>
+          <t>2033 год</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>2033 год</t>
+          <t>2034 год</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>2034 год</t>
+          <t>2035 год</t>
         </is>
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>2035 год</t>
+          <t>2036 год</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>2036 год</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>Прирост
 2024-2036</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>style</t>
         </is>
@@ -804,50 +795,49 @@
       <c r="C5" s="7" t="inlineStr"/>
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
+      <c r="F5" s="8" t="n">
+        <v>1913.21</v>
+      </c>
       <c r="G5" s="8" t="n">
-        <v>1913.21</v>
+        <v>1916.31</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1916.31</v>
+        <v>1951.82</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>1951.82</v>
+        <v>1965.52</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>1965.52</v>
+        <v>1968.29</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>1968.29</v>
+        <v>2087.12</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>2087.12</v>
+        <v>2087.58</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>2087.58</v>
+        <v>2087.78</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>2087.78</v>
+        <v>2087.98</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>2087.98</v>
+        <v>2088.18</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>2088.18</v>
+        <v>2088.38</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>2088.38</v>
+        <v>2088.53</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>2088.53</v>
+        <v>2088.68</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>2088.68</v>
-      </c>
-      <c r="T5" s="8" t="n">
         <v>175.47</v>
       </c>
-      <c r="U5" s="7" t="inlineStr">
+      <c r="T5" s="7" t="inlineStr">
         <is>
           <t>s01</t>
         </is>
@@ -863,50 +853,49 @@
       <c r="C6" s="10" t="inlineStr"/>
       <c r="D6" s="10" t="inlineStr"/>
       <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
+      <c r="F6" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>2</v>
+        <v>7.68</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>7.68</v>
+        <v>27.84</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>27.84</v>
+        <v>1161.44</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>1161.44</v>
+        <v>1963.19</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>1963.19</v>
+        <v>2067.59</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>2067.59</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>2067.59</v>
+        <v>2338.89</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>2338.89</v>
+        <v>2336.69</v>
       </c>
       <c r="P6" s="11" t="n">
-        <v>2336.69</v>
+        <v>2334.09</v>
       </c>
       <c r="Q6" s="11" t="n">
-        <v>2334.09</v>
+        <v>2332.19</v>
       </c>
       <c r="R6" s="11" t="n">
-        <v>2332.19</v>
+        <v>2330.49</v>
       </c>
       <c r="S6" s="11" t="n">
         <v>2330.49</v>
       </c>
-      <c r="T6" s="11" t="n">
-        <v>2330.49</v>
-      </c>
-      <c r="U6" s="10" t="inlineStr">
+      <c r="T6" s="10" t="inlineStr">
         <is>
           <t>s03</t>
         </is>
@@ -922,24 +911,26 @@
       <c r="C7" s="13" t="inlineStr"/>
       <c r="D7" s="13" t="inlineStr"/>
       <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="13" t="inlineStr"/>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>2</v>
+        <v>7.68</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>7.68</v>
+        <v>27.84</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>27.84</v>
+        <v>143.6</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>143.6</v>
+        <v>273.39</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>273.39</v>
+        <v>377.79</v>
       </c>
       <c r="M7" s="14" t="n">
         <v>377.79</v>
@@ -948,24 +939,21 @@
         <v>377.79</v>
       </c>
       <c r="O7" s="14" t="n">
-        <v>377.79</v>
+        <v>375.59</v>
       </c>
       <c r="P7" s="14" t="n">
-        <v>375.59</v>
+        <v>372.99</v>
       </c>
       <c r="Q7" s="14" t="n">
-        <v>372.99</v>
+        <v>371.09</v>
       </c>
       <c r="R7" s="14" t="n">
-        <v>371.09</v>
+        <v>369.39</v>
       </c>
       <c r="S7" s="14" t="n">
         <v>369.39</v>
       </c>
-      <c r="T7" s="14" t="n">
-        <v>369.39</v>
-      </c>
-      <c r="U7" s="13" t="inlineStr">
+      <c r="T7" s="13" t="inlineStr">
         <is>
           <t>s031</t>
         </is>
@@ -981,7 +969,9 @@
       <c r="C8" s="13" t="inlineStr"/>
       <c r="D8" s="13" t="inlineStr"/>
       <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="13" t="inlineStr"/>
+      <c r="F8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="G8" s="14" t="n">
         <v>0</v>
       </c>
@@ -992,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>0</v>
+        <v>1017.84</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>1017.84</v>
+        <v>1689.8</v>
       </c>
       <c r="L8" s="14" t="n">
         <v>1689.8</v>
@@ -1004,7 +994,7 @@
         <v>1689.8</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>1689.8</v>
+        <v>1961.1</v>
       </c>
       <c r="O8" s="14" t="n">
         <v>1961.1</v>
@@ -1021,10 +1011,7 @@
       <c r="S8" s="14" t="n">
         <v>1961.1</v>
       </c>
-      <c r="T8" s="14" t="n">
-        <v>1961.1</v>
-      </c>
-      <c r="U8" s="13" t="inlineStr">
+      <c r="T8" s="13" t="inlineStr">
         <is>
           <t>s051</t>
         </is>
@@ -1040,24 +1027,26 @@
       <c r="C9" s="16" t="inlineStr"/>
       <c r="D9" s="16" t="inlineStr"/>
       <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
+      <c r="F9" s="17" t="n">
+        <v>2.34</v>
+      </c>
       <c r="G9" s="17" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>2.55</v>
+        <v>6.97</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>6.97</v>
+        <v>15.21</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>15.21</v>
+        <v>155.47</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>155.47</v>
+        <v>233.81</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>233.81</v>
+        <v>338.21</v>
       </c>
       <c r="M9" s="17" t="n">
         <v>338.21</v>
@@ -1078,12 +1067,9 @@
         <v>338.21</v>
       </c>
       <c r="S9" s="17" t="n">
-        <v>338.21</v>
-      </c>
-      <c r="T9" s="17" t="n">
         <v>335.87</v>
       </c>
-      <c r="U9" s="16" t="inlineStr">
+      <c r="T9" s="16" t="inlineStr">
         <is>
           <t>s06</t>
         </is>
@@ -1116,50 +1102,49 @@
       <c r="C10" s="19" t="inlineStr"/>
       <c r="D10" s="19" t="inlineStr"/>
       <c r="E10" s="19" t="inlineStr"/>
-      <c r="F10" s="19" t="inlineStr"/>
+      <c r="F10" s="20" t="n">
+        <v>1913.21</v>
+      </c>
       <c r="G10" s="20" t="n">
-        <v>1913.21</v>
+        <v>1918.31</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>1918.31</v>
+        <v>1959.5</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>1959.5</v>
+        <v>1993.36</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>1993.36</v>
+        <v>2111.89</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>2111.89</v>
+        <v>2360.51</v>
       </c>
       <c r="L10" s="20" t="n">
-        <v>2360.51</v>
+        <v>2465.37</v>
       </c>
       <c r="M10" s="20" t="n">
-        <v>2465.37</v>
+        <v>2465.57</v>
       </c>
       <c r="N10" s="20" t="n">
-        <v>2465.57</v>
+        <v>2465.77</v>
       </c>
       <c r="O10" s="20" t="n">
-        <v>2465.77</v>
+        <v>2463.77</v>
       </c>
       <c r="P10" s="20" t="n">
-        <v>2463.77</v>
+        <v>2461.37</v>
       </c>
       <c r="Q10" s="20" t="n">
-        <v>2461.37</v>
+        <v>2459.62</v>
       </c>
       <c r="R10" s="20" t="n">
-        <v>2459.62</v>
+        <v>2458.07</v>
       </c>
       <c r="S10" s="20" t="n">
-        <v>2458.07</v>
-      </c>
-      <c r="T10" s="20" t="n">
         <v>544.86</v>
       </c>
-      <c r="U10" s="19" t="inlineStr">
+      <c r="T10" s="19" t="inlineStr">
         <is>
           <t>s02</t>
         </is>
@@ -1192,50 +1177,49 @@
       <c r="C11" s="19" t="inlineStr"/>
       <c r="D11" s="19" t="inlineStr"/>
       <c r="E11" s="19" t="inlineStr"/>
-      <c r="F11" s="19" t="inlineStr"/>
+      <c r="F11" s="20" t="n">
+        <v>1913.21</v>
+      </c>
       <c r="G11" s="20" t="n">
-        <v>1913.21</v>
+        <v>1918.31</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>1918.31</v>
+        <v>1959.5</v>
       </c>
       <c r="I11" s="20" t="n">
-        <v>1959.5</v>
+        <v>1993.36</v>
       </c>
       <c r="J11" s="20" t="n">
-        <v>1993.36</v>
+        <v>3129.73</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>3129.73</v>
+        <v>4050.31</v>
       </c>
       <c r="L11" s="20" t="n">
-        <v>4050.31</v>
+        <v>4155.17</v>
       </c>
       <c r="M11" s="20" t="n">
-        <v>4155.17</v>
+        <v>4155.37</v>
       </c>
       <c r="N11" s="20" t="n">
-        <v>4155.37</v>
+        <v>4426.87</v>
       </c>
       <c r="O11" s="20" t="n">
-        <v>4426.87</v>
+        <v>4424.87</v>
       </c>
       <c r="P11" s="20" t="n">
-        <v>4424.87</v>
+        <v>4422.47</v>
       </c>
       <c r="Q11" s="20" t="n">
-        <v>4422.47</v>
+        <v>4420.72</v>
       </c>
       <c r="R11" s="20" t="n">
-        <v>4420.72</v>
+        <v>4419.17</v>
       </c>
       <c r="S11" s="20" t="n">
-        <v>4419.17</v>
-      </c>
-      <c r="T11" s="20" t="n">
         <v>2505.96</v>
       </c>
-      <c r="U11" s="19" t="inlineStr">
+      <c r="T11" s="19" t="inlineStr">
         <is>
           <t>s02</t>
         </is>
@@ -1251,50 +1235,49 @@
       <c r="C12" s="7" t="inlineStr"/>
       <c r="D12" s="7" t="inlineStr"/>
       <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="n">
+        <v>1913.21</v>
+      </c>
       <c r="G12" s="8" t="n">
-        <v>1913.21</v>
+        <v>1916.31</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>1916.31</v>
+        <v>1951.82</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>1951.82</v>
+        <v>1965.52</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>1965.52</v>
+        <v>1968.29</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>1968.29</v>
+        <v>2087.12</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>2087.12</v>
+        <v>2087.58</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>2087.58</v>
+        <v>2087.78</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>2087.78</v>
+        <v>2087.98</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>2087.98</v>
+        <v>2088.18</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>2088.18</v>
+        <v>2088.38</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>2088.38</v>
+        <v>2088.53</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>2088.53</v>
+        <v>2088.68</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>2088.68</v>
-      </c>
-      <c r="T12" s="8" t="n">
         <v>175.47</v>
       </c>
-      <c r="U12" s="7" t="inlineStr">
+      <c r="T12" s="7" t="inlineStr">
         <is>
           <t>s01</t>
         </is>
@@ -1310,50 +1293,49 @@
       <c r="C13" s="10" t="inlineStr"/>
       <c r="D13" s="10" t="inlineStr"/>
       <c r="E13" s="10" t="inlineStr"/>
-      <c r="F13" s="10" t="inlineStr"/>
+      <c r="F13" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G13" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>2</v>
+        <v>7.68</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>7.68</v>
+        <v>27.84</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>27.84</v>
+        <v>1161.44</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>1161.44</v>
+        <v>1963.19</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>1963.19</v>
+        <v>2067.59</v>
       </c>
       <c r="M13" s="11" t="n">
         <v>2067.59</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>2067.59</v>
+        <v>2338.89</v>
       </c>
       <c r="O13" s="11" t="n">
-        <v>2338.89</v>
+        <v>2336.69</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>2336.69</v>
+        <v>2334.09</v>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>2334.09</v>
+        <v>2332.19</v>
       </c>
       <c r="R13" s="11" t="n">
-        <v>2332.19</v>
+        <v>2330.49</v>
       </c>
       <c r="S13" s="11" t="n">
         <v>2330.49</v>
       </c>
-      <c r="T13" s="11" t="n">
-        <v>2330.49</v>
-      </c>
-      <c r="U13" s="10" t="inlineStr">
+      <c r="T13" s="10" t="inlineStr">
         <is>
           <t>s03</t>
         </is>
@@ -1369,24 +1351,26 @@
       <c r="C14" s="13" t="inlineStr"/>
       <c r="D14" s="13" t="inlineStr"/>
       <c r="E14" s="13" t="inlineStr"/>
-      <c r="F14" s="13" t="inlineStr"/>
+      <c r="F14" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>2</v>
+        <v>7.68</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>7.68</v>
+        <v>27.84</v>
       </c>
       <c r="J14" s="14" t="n">
-        <v>27.84</v>
+        <v>143.6</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>143.6</v>
+        <v>273.39</v>
       </c>
       <c r="L14" s="14" t="n">
-        <v>273.39</v>
+        <v>377.79</v>
       </c>
       <c r="M14" s="14" t="n">
         <v>377.79</v>
@@ -1395,24 +1379,21 @@
         <v>377.79</v>
       </c>
       <c r="O14" s="14" t="n">
-        <v>377.79</v>
+        <v>375.59</v>
       </c>
       <c r="P14" s="14" t="n">
-        <v>375.59</v>
+        <v>372.99</v>
       </c>
       <c r="Q14" s="14" t="n">
-        <v>372.99</v>
+        <v>371.09</v>
       </c>
       <c r="R14" s="14" t="n">
-        <v>371.09</v>
+        <v>369.39</v>
       </c>
       <c r="S14" s="14" t="n">
         <v>369.39</v>
       </c>
-      <c r="T14" s="14" t="n">
-        <v>369.39</v>
-      </c>
-      <c r="U14" s="13" t="inlineStr">
+      <c r="T14" s="13" t="inlineStr">
         <is>
           <t>s031</t>
         </is>
@@ -1428,7 +1409,9 @@
       <c r="C15" s="13" t="inlineStr"/>
       <c r="D15" s="13" t="inlineStr"/>
       <c r="E15" s="13" t="inlineStr"/>
-      <c r="F15" s="13" t="inlineStr"/>
+      <c r="F15" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="G15" s="14" t="n">
         <v>0</v>
       </c>
@@ -1439,10 +1422,10 @@
         <v>0</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>0</v>
+        <v>1017.84</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>1017.84</v>
+        <v>1689.8</v>
       </c>
       <c r="L15" s="14" t="n">
         <v>1689.8</v>
@@ -1451,7 +1434,7 @@
         <v>1689.8</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>1689.8</v>
+        <v>1961.1</v>
       </c>
       <c r="O15" s="14" t="n">
         <v>1961.1</v>
@@ -1468,10 +1451,7 @@
       <c r="S15" s="14" t="n">
         <v>1961.1</v>
       </c>
-      <c r="T15" s="14" t="n">
-        <v>1961.1</v>
-      </c>
-      <c r="U15" s="13" t="inlineStr">
+      <c r="T15" s="13" t="inlineStr">
         <is>
           <t>s051</t>
         </is>
@@ -1487,24 +1467,26 @@
       <c r="C16" s="16" t="inlineStr"/>
       <c r="D16" s="16" t="inlineStr"/>
       <c r="E16" s="16" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr"/>
+      <c r="F16" s="17" t="n">
+        <v>2.34</v>
+      </c>
       <c r="G16" s="17" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="H16" s="17" t="n">
-        <v>2.55</v>
+        <v>6.97</v>
       </c>
       <c r="I16" s="17" t="n">
-        <v>6.97</v>
+        <v>15.21</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>15.21</v>
+        <v>155.47</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>155.47</v>
+        <v>233.81</v>
       </c>
       <c r="L16" s="17" t="n">
-        <v>233.81</v>
+        <v>338.21</v>
       </c>
       <c r="M16" s="17" t="n">
         <v>338.21</v>
@@ -1525,12 +1507,9 @@
         <v>338.21</v>
       </c>
       <c r="S16" s="17" t="n">
-        <v>338.21</v>
-      </c>
-      <c r="T16" s="17" t="n">
         <v>335.87</v>
       </c>
-      <c r="U16" s="16" t="inlineStr">
+      <c r="T16" s="16" t="inlineStr">
         <is>
           <t>s06</t>
         </is>
@@ -1563,50 +1542,49 @@
       <c r="C17" s="19" t="inlineStr"/>
       <c r="D17" s="19" t="inlineStr"/>
       <c r="E17" s="19" t="inlineStr"/>
-      <c r="F17" s="19" t="inlineStr"/>
+      <c r="F17" s="20" t="n">
+        <v>1913.21</v>
+      </c>
       <c r="G17" s="20" t="n">
-        <v>1913.21</v>
+        <v>1918.31</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>1918.31</v>
+        <v>1959.5</v>
       </c>
       <c r="I17" s="20" t="n">
-        <v>1959.5</v>
+        <v>1993.36</v>
       </c>
       <c r="J17" s="20" t="n">
-        <v>1993.36</v>
+        <v>2111.89</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>2111.89</v>
+        <v>2360.51</v>
       </c>
       <c r="L17" s="20" t="n">
-        <v>2360.51</v>
+        <v>2465.37</v>
       </c>
       <c r="M17" s="20" t="n">
-        <v>2465.37</v>
+        <v>2465.57</v>
       </c>
       <c r="N17" s="20" t="n">
-        <v>2465.57</v>
+        <v>2465.77</v>
       </c>
       <c r="O17" s="20" t="n">
-        <v>2465.77</v>
+        <v>2463.77</v>
       </c>
       <c r="P17" s="20" t="n">
-        <v>2463.77</v>
+        <v>2461.37</v>
       </c>
       <c r="Q17" s="20" t="n">
-        <v>2461.37</v>
+        <v>2459.62</v>
       </c>
       <c r="R17" s="20" t="n">
-        <v>2459.62</v>
+        <v>2458.07</v>
       </c>
       <c r="S17" s="20" t="n">
-        <v>2458.07</v>
-      </c>
-      <c r="T17" s="20" t="n">
         <v>544.86</v>
       </c>
-      <c r="U17" s="19" t="inlineStr">
+      <c r="T17" s="19" t="inlineStr">
         <is>
           <t>s02</t>
         </is>
@@ -1639,50 +1617,49 @@
       <c r="C18" s="19" t="inlineStr"/>
       <c r="D18" s="19" t="inlineStr"/>
       <c r="E18" s="19" t="inlineStr"/>
-      <c r="F18" s="19" t="inlineStr"/>
+      <c r="F18" s="20" t="n">
+        <v>1913.21</v>
+      </c>
       <c r="G18" s="20" t="n">
-        <v>1913.21</v>
+        <v>1918.31</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>1918.31</v>
+        <v>1959.5</v>
       </c>
       <c r="I18" s="20" t="n">
-        <v>1959.5</v>
+        <v>1993.36</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>1993.36</v>
+        <v>3129.73</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>3129.73</v>
+        <v>4050.31</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>4050.31</v>
+        <v>4155.17</v>
       </c>
       <c r="M18" s="20" t="n">
-        <v>4155.17</v>
+        <v>4155.37</v>
       </c>
       <c r="N18" s="20" t="n">
-        <v>4155.37</v>
+        <v>4426.87</v>
       </c>
       <c r="O18" s="20" t="n">
-        <v>4426.87</v>
+        <v>4424.87</v>
       </c>
       <c r="P18" s="20" t="n">
-        <v>4424.87</v>
+        <v>4422.47</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>4422.47</v>
+        <v>4420.72</v>
       </c>
       <c r="R18" s="20" t="n">
-        <v>4420.72</v>
+        <v>4419.17</v>
       </c>
       <c r="S18" s="20" t="n">
-        <v>4419.17</v>
-      </c>
-      <c r="T18" s="20" t="n">
         <v>2505.96</v>
       </c>
-      <c r="U18" s="19" t="inlineStr">
+      <c r="T18" s="19" t="inlineStr">
         <is>
           <t>s02</t>
         </is>
@@ -1698,50 +1675,49 @@
       <c r="C19" s="22" t="inlineStr"/>
       <c r="D19" s="22" t="inlineStr"/>
       <c r="E19" s="22" t="inlineStr"/>
-      <c r="F19" s="22" t="inlineStr"/>
+      <c r="F19" s="23" t="n">
+        <v>1913.21</v>
+      </c>
       <c r="G19" s="23" t="n">
-        <v>1913.21</v>
+        <v>1916.31</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>1916.31</v>
+        <v>1951.82</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>1951.82</v>
+        <v>1965.52</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>1965.52</v>
+        <v>1968.29</v>
       </c>
       <c r="K19" s="23" t="n">
-        <v>1968.29</v>
+        <v>2087.12</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>2087.12</v>
+        <v>2087.58</v>
       </c>
       <c r="M19" s="23" t="n">
-        <v>2087.58</v>
+        <v>2087.78</v>
       </c>
       <c r="N19" s="23" t="n">
-        <v>2087.78</v>
+        <v>2087.98</v>
       </c>
       <c r="O19" s="23" t="n">
-        <v>2087.98</v>
+        <v>2088.18</v>
       </c>
       <c r="P19" s="23" t="n">
-        <v>2088.18</v>
+        <v>2088.38</v>
       </c>
       <c r="Q19" s="23" t="n">
-        <v>2088.38</v>
+        <v>2088.53</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>2088.53</v>
+        <v>2088.68</v>
       </c>
       <c r="S19" s="23" t="n">
-        <v>2088.68</v>
-      </c>
-      <c r="T19" s="23" t="n">
         <v>175.47</v>
       </c>
-      <c r="U19" s="22" t="inlineStr">
+      <c r="T19" s="22" t="inlineStr">
         <is>
           <t>s04</t>
         </is>
@@ -1768,19 +1744,17 @@
           <t>V</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>0 - действующие потребители</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="n">
+      <c r="E20" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="F20" s="26" t="n">
+        <v>324.83</v>
+      </c>
       <c r="G20" s="26" t="n">
-        <v>324.83</v>
+        <v>364.03</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>364.03</v>
+        <v>365</v>
       </c>
       <c r="I20" s="26" t="n">
         <v>365</v>
@@ -1813,12 +1787,9 @@
         <v>365</v>
       </c>
       <c r="S20" s="26" t="n">
-        <v>365</v>
-      </c>
-      <c r="T20" s="26" t="n">
         <v>40.17</v>
       </c>
-      <c r="U20" s="25" t="inlineStr">
+      <c r="T20" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -1845,19 +1816,17 @@
           <t>V</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>0 - действующие потребители</t>
-        </is>
-      </c>
-      <c r="F21" s="25" t="n">
+      <c r="E21" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="F21" s="26" t="n">
+        <v>816.51</v>
+      </c>
       <c r="G21" s="26" t="n">
-        <v>816.51</v>
+        <v>765.89</v>
       </c>
       <c r="H21" s="26" t="n">
-        <v>765.89</v>
+        <v>773.45</v>
       </c>
       <c r="I21" s="26" t="n">
         <v>773.45</v>
@@ -1866,7 +1835,7 @@
         <v>773.45</v>
       </c>
       <c r="K21" s="26" t="n">
-        <v>773.45</v>
+        <v>882.12</v>
       </c>
       <c r="L21" s="26" t="n">
         <v>882.12</v>
@@ -1890,12 +1859,9 @@
         <v>882.12</v>
       </c>
       <c r="S21" s="26" t="n">
-        <v>882.12</v>
-      </c>
-      <c r="T21" s="26" t="n">
         <v>65.61</v>
       </c>
-      <c r="U21" s="25" t="inlineStr">
+      <c r="T21" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -1922,28 +1888,26 @@
           <t>V</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>0 - действующие потребители</t>
-        </is>
-      </c>
-      <c r="F22" s="25" t="n">
+      <c r="E22" s="25" t="n">
         <v>11</v>
       </c>
+      <c r="F22" s="26" t="n">
+        <v>23.9</v>
+      </c>
       <c r="G22" s="26" t="n">
-        <v>23.9</v>
+        <v>37.54</v>
       </c>
       <c r="H22" s="26" t="n">
-        <v>37.54</v>
+        <v>38.4</v>
       </c>
       <c r="I22" s="26" t="n">
-        <v>38.4</v>
+        <v>38.41</v>
       </c>
       <c r="J22" s="26" t="n">
         <v>38.41</v>
       </c>
       <c r="K22" s="26" t="n">
-        <v>38.41</v>
+        <v>38.8</v>
       </c>
       <c r="L22" s="26" t="n">
         <v>38.8</v>
@@ -1967,12 +1931,9 @@
         <v>38.8</v>
       </c>
       <c r="S22" s="26" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="T22" s="26" t="n">
         <v>14.9</v>
       </c>
-      <c r="U22" s="25" t="inlineStr">
+      <c r="T22" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -1999,19 +1960,17 @@
           <t>V</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
-        <is>
-          <t>0 - действующие потребители</t>
-        </is>
-      </c>
-      <c r="F23" s="25" t="n">
+      <c r="E23" s="25" t="n">
         <v>18</v>
       </c>
+      <c r="F23" s="26" t="n">
+        <v>0.8100000000000001</v>
+      </c>
       <c r="G23" s="26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H23" s="26" t="n">
-        <v>0.68</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="I23" s="26" t="n">
         <v>0.8200000000000001</v>
@@ -2044,12 +2003,9 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="S23" s="26" t="n">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="T23" s="26" t="n">
         <v>0.01</v>
       </c>
-      <c r="U23" s="25" t="inlineStr">
+      <c r="T23" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2065,50 +2021,49 @@
       <c r="C24" s="25" t="inlineStr"/>
       <c r="D24" s="25" t="inlineStr"/>
       <c r="E24" s="25" t="inlineStr"/>
-      <c r="F24" s="25" t="inlineStr"/>
+      <c r="F24" s="26" t="n">
+        <v>747.16</v>
+      </c>
       <c r="G24" s="26" t="n">
-        <v>747.16</v>
+        <v>748.17</v>
       </c>
       <c r="H24" s="26" t="n">
-        <v>748.17</v>
+        <v>774.15</v>
       </c>
       <c r="I24" s="26" t="n">
-        <v>774.15</v>
+        <v>787.84</v>
       </c>
       <c r="J24" s="26" t="n">
-        <v>787.84</v>
+        <v>790.61</v>
       </c>
       <c r="K24" s="26" t="n">
-        <v>790.61</v>
+        <v>800.38</v>
       </c>
       <c r="L24" s="26" t="n">
-        <v>800.38</v>
+        <v>800.84</v>
       </c>
       <c r="M24" s="26" t="n">
-        <v>800.84</v>
+        <v>801.04</v>
       </c>
       <c r="N24" s="26" t="n">
-        <v>801.04</v>
+        <v>801.24</v>
       </c>
       <c r="O24" s="26" t="n">
-        <v>801.24</v>
+        <v>801.4400000000001</v>
       </c>
       <c r="P24" s="26" t="n">
-        <v>801.4400000000001</v>
+        <v>801.64</v>
       </c>
       <c r="Q24" s="26" t="n">
-        <v>801.64</v>
+        <v>801.79</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>801.79</v>
+        <v>801.9400000000001</v>
       </c>
       <c r="S24" s="26" t="n">
-        <v>801.9400000000001</v>
-      </c>
-      <c r="T24" s="26" t="n">
         <v>54.78</v>
       </c>
-      <c r="U24" s="25" t="inlineStr">
+      <c r="T24" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2124,24 +2079,26 @@
       <c r="C25" s="22" t="inlineStr"/>
       <c r="D25" s="22" t="inlineStr"/>
       <c r="E25" s="22" t="inlineStr"/>
-      <c r="F25" s="22" t="inlineStr"/>
+      <c r="F25" s="23" t="n">
+        <v>0</v>
+      </c>
       <c r="G25" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>2</v>
+        <v>7.68</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>7.68</v>
+        <v>27.84</v>
       </c>
       <c r="J25" s="23" t="n">
-        <v>27.84</v>
+        <v>143.6</v>
       </c>
       <c r="K25" s="23" t="n">
-        <v>143.6</v>
+        <v>273.39</v>
       </c>
       <c r="L25" s="23" t="n">
-        <v>273.39</v>
+        <v>377.79</v>
       </c>
       <c r="M25" s="23" t="n">
         <v>377.79</v>
@@ -2150,24 +2107,21 @@
         <v>377.79</v>
       </c>
       <c r="O25" s="23" t="n">
-        <v>377.79</v>
+        <v>375.59</v>
       </c>
       <c r="P25" s="23" t="n">
-        <v>375.59</v>
+        <v>372.99</v>
       </c>
       <c r="Q25" s="23" t="n">
-        <v>372.99</v>
+        <v>371.09</v>
       </c>
       <c r="R25" s="23" t="n">
-        <v>371.09</v>
+        <v>369.39</v>
       </c>
       <c r="S25" s="23" t="n">
         <v>369.39</v>
       </c>
-      <c r="T25" s="23" t="n">
-        <v>369.39</v>
-      </c>
-      <c r="U25" s="22" t="inlineStr">
+      <c r="T25" s="22" t="inlineStr">
         <is>
           <t>s04</t>
         </is>
@@ -2194,14 +2148,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>2 - средняя вероятность реализации проекта</t>
-        </is>
-      </c>
-      <c r="F26" s="25" t="n">
+      <c r="E26" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="F26" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G26" s="26" t="n">
         <v>0</v>
       </c>
@@ -2218,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M26" s="26" t="n">
         <v>17</v>
@@ -2241,10 +2193,7 @@
       <c r="S26" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="T26" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="U26" s="25" t="inlineStr">
+      <c r="T26" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2271,14 +2220,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>2 - средняя вероятность реализации проекта</t>
-        </is>
-      </c>
-      <c r="F27" s="25" t="n">
+      <c r="E27" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="F27" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G27" s="26" t="n">
         <v>0</v>
       </c>
@@ -2289,13 +2236,13 @@
         <v>0</v>
       </c>
       <c r="J27" s="26" t="n">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="K27" s="26" t="n">
         <v>56.4</v>
       </c>
       <c r="L27" s="26" t="n">
-        <v>56.4</v>
+        <v>134</v>
       </c>
       <c r="M27" s="26" t="n">
         <v>134</v>
@@ -2318,10 +2265,7 @@
       <c r="S27" s="26" t="n">
         <v>134</v>
       </c>
-      <c r="T27" s="26" t="n">
-        <v>134</v>
-      </c>
-      <c r="U27" s="25" t="inlineStr">
+      <c r="T27" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2348,14 +2292,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>2 - средняя вероятность реализации проекта</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="n">
+      <c r="E28" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="F28" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G28" s="26" t="n">
         <v>0</v>
       </c>
@@ -2366,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K28" s="26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L28" s="26" t="n">
         <v>100</v>
@@ -2395,10 +2337,7 @@
       <c r="S28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="T28" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="U28" s="25" t="inlineStr">
+      <c r="T28" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2425,14 +2364,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
-        <is>
-          <t>2 - средняя вероятность реализации проекта</t>
-        </is>
-      </c>
-      <c r="F29" s="25" t="n">
+      <c r="E29" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="F29" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G29" s="26" t="n">
         <v>0</v>
       </c>
@@ -2446,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="26" t="n">
-        <v>0</v>
+        <v>50.4</v>
       </c>
       <c r="L29" s="26" t="n">
         <v>50.4</v>
@@ -2472,10 +2409,7 @@
       <c r="S29" s="26" t="n">
         <v>50.4</v>
       </c>
-      <c r="T29" s="26" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="U29" s="25" t="inlineStr">
+      <c r="T29" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2502,28 +2436,26 @@
           <t>V</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
-        <is>
-          <t>1 - высокая вероятность реализации проекта</t>
-        </is>
-      </c>
-      <c r="F30" s="25" t="n">
+      <c r="E30" s="25" t="n">
         <v>11</v>
       </c>
+      <c r="F30" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G30" s="26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="H30" s="26" t="n">
         <v>1.68</v>
       </c>
       <c r="I30" s="26" t="n">
-        <v>1.68</v>
+        <v>12.59</v>
       </c>
       <c r="J30" s="26" t="n">
         <v>12.59</v>
       </c>
       <c r="K30" s="26" t="n">
-        <v>12.59</v>
+        <v>14</v>
       </c>
       <c r="L30" s="26" t="n">
         <v>14</v>
@@ -2535,24 +2467,21 @@
         <v>14</v>
       </c>
       <c r="O30" s="26" t="n">
-        <v>14</v>
+        <v>11.8</v>
       </c>
       <c r="P30" s="26" t="n">
-        <v>11.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q30" s="26" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>7.3</v>
+        <v>5.6</v>
       </c>
       <c r="S30" s="26" t="n">
         <v>5.6</v>
       </c>
-      <c r="T30" s="26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="U30" s="25" t="inlineStr">
+      <c r="T30" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2568,24 +2497,26 @@
       <c r="C31" s="25" t="inlineStr"/>
       <c r="D31" s="25" t="inlineStr"/>
       <c r="E31" s="25" t="inlineStr"/>
-      <c r="F31" s="25" t="inlineStr"/>
+      <c r="F31" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G31" s="26" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="H31" s="26" t="n">
-        <v>0.32</v>
+        <v>6</v>
       </c>
       <c r="I31" s="26" t="n">
-        <v>6</v>
+        <v>15.25</v>
       </c>
       <c r="J31" s="26" t="n">
-        <v>15.25</v>
+        <v>24.61</v>
       </c>
       <c r="K31" s="26" t="n">
-        <v>24.61</v>
+        <v>52.59</v>
       </c>
       <c r="L31" s="26" t="n">
-        <v>52.59</v>
+        <v>62.39</v>
       </c>
       <c r="M31" s="26" t="n">
         <v>62.39</v>
@@ -2608,10 +2539,7 @@
       <c r="S31" s="26" t="n">
         <v>62.39</v>
       </c>
-      <c r="T31" s="26" t="n">
-        <v>62.39</v>
-      </c>
-      <c r="U31" s="25" t="inlineStr">
+      <c r="T31" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2627,7 +2555,9 @@
       <c r="C32" s="22" t="inlineStr"/>
       <c r="D32" s="22" t="inlineStr"/>
       <c r="E32" s="22" t="inlineStr"/>
-      <c r="F32" s="22" t="inlineStr"/>
+      <c r="F32" s="23" t="n">
+        <v>0</v>
+      </c>
       <c r="G32" s="23" t="n">
         <v>0</v>
       </c>
@@ -2638,10 +2568,10 @@
         <v>0</v>
       </c>
       <c r="J32" s="23" t="n">
-        <v>0</v>
+        <v>1017.84</v>
       </c>
       <c r="K32" s="23" t="n">
-        <v>1017.84</v>
+        <v>1689.8</v>
       </c>
       <c r="L32" s="23" t="n">
         <v>1689.8</v>
@@ -2650,7 +2580,7 @@
         <v>1689.8</v>
       </c>
       <c r="N32" s="23" t="n">
-        <v>1689.8</v>
+        <v>1961.1</v>
       </c>
       <c r="O32" s="23" t="n">
         <v>1961.1</v>
@@ -2667,10 +2597,7 @@
       <c r="S32" s="23" t="n">
         <v>1961.1</v>
       </c>
-      <c r="T32" s="23" t="n">
-        <v>1961.1</v>
-      </c>
-      <c r="U32" s="22" t="inlineStr">
+      <c r="T32" s="22" t="inlineStr">
         <is>
           <t>s04</t>
         </is>
@@ -2697,14 +2624,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>3 - низкая вероятность реализации проекта</t>
-        </is>
-      </c>
-      <c r="F33" s="25" t="n">
+      <c r="E33" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="F33" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" s="26" t="n">
         <v>0</v>
       </c>
@@ -2715,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K33" s="26" t="n">
         <v>25</v>
@@ -2744,10 +2669,7 @@
       <c r="S33" s="26" t="n">
         <v>25</v>
       </c>
-      <c r="T33" s="26" t="n">
-        <v>25</v>
-      </c>
-      <c r="U33" s="25" t="inlineStr">
+      <c r="T33" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2774,14 +2696,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>3 - низкая вероятность реализации проекта</t>
-        </is>
-      </c>
-      <c r="F34" s="25" t="n">
+      <c r="E34" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="F34" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G34" s="26" t="n">
         <v>0</v>
       </c>
@@ -2804,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="26" t="n">
-        <v>0</v>
+        <v>271.3</v>
       </c>
       <c r="O34" s="26" t="n">
         <v>271.3</v>
@@ -2821,10 +2741,7 @@
       <c r="S34" s="26" t="n">
         <v>271.3</v>
       </c>
-      <c r="T34" s="26" t="n">
-        <v>271.3</v>
-      </c>
-      <c r="U34" s="25" t="inlineStr">
+      <c r="T34" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2851,14 +2768,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E35" s="25" t="inlineStr">
-        <is>
-          <t>3 - низкая вероятность реализации проекта</t>
-        </is>
-      </c>
-      <c r="F35" s="25" t="n">
+      <c r="E35" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="F35" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G35" s="26" t="n">
         <v>0</v>
       </c>
@@ -2869,10 +2784,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="26" t="n">
-        <v>0</v>
+        <v>554.8</v>
       </c>
       <c r="K35" s="26" t="n">
-        <v>554.8</v>
+        <v>788.4</v>
       </c>
       <c r="L35" s="26" t="n">
         <v>788.4</v>
@@ -2898,10 +2813,7 @@
       <c r="S35" s="26" t="n">
         <v>788.4</v>
       </c>
-      <c r="T35" s="26" t="n">
-        <v>788.4</v>
-      </c>
-      <c r="U35" s="25" t="inlineStr">
+      <c r="T35" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2928,14 +2840,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
-        <is>
-          <t>3 - низкая вероятность реализации проекта</t>
-        </is>
-      </c>
-      <c r="F36" s="25" t="n">
+      <c r="E36" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="F36" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G36" s="26" t="n">
         <v>0</v>
       </c>
@@ -2946,10 +2856,10 @@
         <v>0</v>
       </c>
       <c r="J36" s="26" t="n">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="K36" s="26" t="n">
-        <v>438</v>
+        <v>876</v>
       </c>
       <c r="L36" s="26" t="n">
         <v>876</v>
@@ -2975,10 +2885,7 @@
       <c r="S36" s="26" t="n">
         <v>876</v>
       </c>
-      <c r="T36" s="26" t="n">
-        <v>876</v>
-      </c>
-      <c r="U36" s="25" t="inlineStr">
+      <c r="T36" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -2994,7 +2901,9 @@
       <c r="C37" s="25" t="inlineStr"/>
       <c r="D37" s="25" t="inlineStr"/>
       <c r="E37" s="25" t="inlineStr"/>
-      <c r="F37" s="25" t="inlineStr"/>
+      <c r="F37" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="G37" s="26" t="n">
         <v>0</v>
       </c>
@@ -3005,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="J37" s="26" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K37" s="26" t="n">
-        <v>0.04</v>
+        <v>0.4</v>
       </c>
       <c r="L37" s="26" t="n">
         <v>0.4</v>
@@ -3034,10 +2943,7 @@
       <c r="S37" s="26" t="n">
         <v>0.4</v>
       </c>
-      <c r="T37" s="26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U37" s="25" t="inlineStr">
+      <c r="T37" s="25" t="inlineStr">
         <is>
           <t>s041</t>
         </is>
@@ -3045,9 +2951,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output.xlsx
+++ b/output.xlsx
@@ -866,34 +866,34 @@
         <v>27.84</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>1161.44</v>
+        <v>1247.04</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>1963.19</v>
+        <v>2048.79</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>2067.59</v>
+        <v>2238.79</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>2067.59</v>
+        <v>2238.79</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>2338.89</v>
+        <v>2510.09</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>2336.69</v>
+        <v>2507.89</v>
       </c>
       <c r="P6" s="11" t="n">
-        <v>2334.09</v>
+        <v>2505.29</v>
       </c>
       <c r="Q6" s="11" t="n">
-        <v>2332.19</v>
+        <v>2503.39</v>
       </c>
       <c r="R6" s="11" t="n">
-        <v>2330.49</v>
+        <v>2501.69</v>
       </c>
       <c r="S6" s="11" t="n">
-        <v>2330.49</v>
+        <v>2501.69</v>
       </c>
       <c r="T6" s="10" t="inlineStr">
         <is>
@@ -924,34 +924,34 @@
         <v>27.84</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>143.6</v>
+        <v>229.2</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>273.39</v>
+        <v>358.99</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>377.79</v>
+        <v>548.99</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>377.79</v>
+        <v>548.99</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>377.79</v>
+        <v>548.99</v>
       </c>
       <c r="O7" s="14" t="n">
-        <v>375.59</v>
+        <v>546.79</v>
       </c>
       <c r="P7" s="14" t="n">
-        <v>372.99</v>
+        <v>544.1900000000001</v>
       </c>
       <c r="Q7" s="14" t="n">
-        <v>371.09</v>
+        <v>542.29</v>
       </c>
       <c r="R7" s="14" t="n">
-        <v>369.39</v>
+        <v>540.59</v>
       </c>
       <c r="S7" s="14" t="n">
-        <v>369.39</v>
+        <v>540.59</v>
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
@@ -1040,34 +1040,34 @@
         <v>15.21</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>155.47</v>
+        <v>241.07</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>233.81</v>
+        <v>319.41</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="N9" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="O9" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="P9" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="S9" s="17" t="n">
-        <v>335.87</v>
+        <v>507.07</v>
       </c>
       <c r="T9" s="16" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         <v>1993.36</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>2111.89</v>
+        <v>2197.49</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>2360.51</v>
+        <v>2446.11</v>
       </c>
       <c r="L10" s="20" t="n">
-        <v>2465.37</v>
+        <v>2636.57</v>
       </c>
       <c r="M10" s="20" t="n">
-        <v>2465.57</v>
+        <v>2636.77</v>
       </c>
       <c r="N10" s="20" t="n">
-        <v>2465.77</v>
+        <v>2636.97</v>
       </c>
       <c r="O10" s="20" t="n">
-        <v>2463.77</v>
+        <v>2634.97</v>
       </c>
       <c r="P10" s="20" t="n">
-        <v>2461.37</v>
+        <v>2632.57</v>
       </c>
       <c r="Q10" s="20" t="n">
-        <v>2459.62</v>
+        <v>2630.82</v>
       </c>
       <c r="R10" s="20" t="n">
-        <v>2458.07</v>
+        <v>2629.27</v>
       </c>
       <c r="S10" s="20" t="n">
-        <v>544.86</v>
+        <v>716.0599999999999</v>
       </c>
       <c r="T10" s="19" t="inlineStr">
         <is>
@@ -1190,34 +1190,34 @@
         <v>1993.36</v>
       </c>
       <c r="J11" s="20" t="n">
-        <v>3129.73</v>
+        <v>3215.33</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>4050.31</v>
+        <v>4135.91</v>
       </c>
       <c r="L11" s="20" t="n">
-        <v>4155.17</v>
+        <v>4326.37</v>
       </c>
       <c r="M11" s="20" t="n">
-        <v>4155.37</v>
+        <v>4326.57</v>
       </c>
       <c r="N11" s="20" t="n">
-        <v>4426.87</v>
+        <v>4598.07</v>
       </c>
       <c r="O11" s="20" t="n">
-        <v>4424.87</v>
+        <v>4596.07</v>
       </c>
       <c r="P11" s="20" t="n">
-        <v>4422.47</v>
+        <v>4593.67</v>
       </c>
       <c r="Q11" s="20" t="n">
-        <v>4420.72</v>
+        <v>4591.92</v>
       </c>
       <c r="R11" s="20" t="n">
-        <v>4419.17</v>
+        <v>4590.37</v>
       </c>
       <c r="S11" s="20" t="n">
-        <v>2505.96</v>
+        <v>2677.16</v>
       </c>
       <c r="T11" s="19" t="inlineStr">
         <is>
@@ -1306,34 +1306,34 @@
         <v>27.84</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>1161.44</v>
+        <v>1247.04</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>1963.19</v>
+        <v>2048.79</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>2067.59</v>
+        <v>2238.79</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>2067.59</v>
+        <v>2238.79</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>2338.89</v>
+        <v>2510.09</v>
       </c>
       <c r="O13" s="11" t="n">
-        <v>2336.69</v>
+        <v>2507.89</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>2334.09</v>
+        <v>2505.29</v>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>2332.19</v>
+        <v>2503.39</v>
       </c>
       <c r="R13" s="11" t="n">
-        <v>2330.49</v>
+        <v>2501.69</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>2330.49</v>
+        <v>2501.69</v>
       </c>
       <c r="T13" s="10" t="inlineStr">
         <is>
@@ -1364,34 +1364,34 @@
         <v>27.84</v>
       </c>
       <c r="J14" s="14" t="n">
-        <v>143.6</v>
+        <v>229.2</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>273.39</v>
+        <v>358.99</v>
       </c>
       <c r="L14" s="14" t="n">
-        <v>377.79</v>
+        <v>548.99</v>
       </c>
       <c r="M14" s="14" t="n">
-        <v>377.79</v>
+        <v>548.99</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>377.79</v>
+        <v>548.99</v>
       </c>
       <c r="O14" s="14" t="n">
-        <v>375.59</v>
+        <v>546.79</v>
       </c>
       <c r="P14" s="14" t="n">
-        <v>372.99</v>
+        <v>544.1900000000001</v>
       </c>
       <c r="Q14" s="14" t="n">
-        <v>371.09</v>
+        <v>542.29</v>
       </c>
       <c r="R14" s="14" t="n">
-        <v>369.39</v>
+        <v>540.59</v>
       </c>
       <c r="S14" s="14" t="n">
-        <v>369.39</v>
+        <v>540.59</v>
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
@@ -1480,34 +1480,34 @@
         <v>15.21</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>155.47</v>
+        <v>241.07</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>233.81</v>
+        <v>319.41</v>
       </c>
       <c r="L16" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="M16" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="N16" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="O16" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="P16" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="R16" s="17" t="n">
-        <v>338.21</v>
+        <v>509.41</v>
       </c>
       <c r="S16" s="17" t="n">
-        <v>335.87</v>
+        <v>507.07</v>
       </c>
       <c r="T16" s="16" t="inlineStr">
         <is>
@@ -1555,34 +1555,34 @@
         <v>1993.36</v>
       </c>
       <c r="J17" s="20" t="n">
-        <v>2111.89</v>
+        <v>2197.49</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>2360.51</v>
+        <v>2446.11</v>
       </c>
       <c r="L17" s="20" t="n">
-        <v>2465.37</v>
+        <v>2636.57</v>
       </c>
       <c r="M17" s="20" t="n">
-        <v>2465.57</v>
+        <v>2636.77</v>
       </c>
       <c r="N17" s="20" t="n">
-        <v>2465.77</v>
+        <v>2636.97</v>
       </c>
       <c r="O17" s="20" t="n">
-        <v>2463.77</v>
+        <v>2634.97</v>
       </c>
       <c r="P17" s="20" t="n">
-        <v>2461.37</v>
+        <v>2632.57</v>
       </c>
       <c r="Q17" s="20" t="n">
-        <v>2459.62</v>
+        <v>2630.82</v>
       </c>
       <c r="R17" s="20" t="n">
-        <v>2458.07</v>
+        <v>2629.27</v>
       </c>
       <c r="S17" s="20" t="n">
-        <v>544.86</v>
+        <v>716.0599999999999</v>
       </c>
       <c r="T17" s="19" t="inlineStr">
         <is>
@@ -1630,34 +1630,34 @@
         <v>1993.36</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>3129.73</v>
+        <v>3215.33</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>4050.31</v>
+        <v>4135.91</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>4155.17</v>
+        <v>4326.37</v>
       </c>
       <c r="M18" s="20" t="n">
-        <v>4155.37</v>
+        <v>4326.57</v>
       </c>
       <c r="N18" s="20" t="n">
-        <v>4426.87</v>
+        <v>4598.07</v>
       </c>
       <c r="O18" s="20" t="n">
-        <v>4424.87</v>
+        <v>4596.07</v>
       </c>
       <c r="P18" s="20" t="n">
-        <v>4422.47</v>
+        <v>4593.67</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>4420.72</v>
+        <v>4591.92</v>
       </c>
       <c r="R18" s="20" t="n">
-        <v>4419.17</v>
+        <v>4590.37</v>
       </c>
       <c r="S18" s="20" t="n">
-        <v>2505.96</v>
+        <v>2677.16</v>
       </c>
       <c r="T18" s="19" t="inlineStr">
         <is>
@@ -1942,68 +1942,54 @@
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>ФГБУ "ЦЖКУ"  Минобороны России ( котельные №97 в/г 135)</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>Минобороны</t>
-        </is>
-      </c>
-      <c r="C23" s="25" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="n">
-        <v>18</v>
-      </c>
+          <t>Действующие потребители</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr"/>
+      <c r="C23" s="25" t="inlineStr"/>
+      <c r="D23" s="25" t="inlineStr"/>
+      <c r="E23" s="25" t="inlineStr"/>
       <c r="F23" s="26" t="n">
-        <v>0.8100000000000001</v>
+        <v>715.65</v>
       </c>
       <c r="G23" s="26" t="n">
-        <v>0.68</v>
+        <v>734.4400000000001</v>
       </c>
       <c r="H23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>757.45</v>
       </c>
       <c r="I23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>771.14</v>
       </c>
       <c r="J23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>771.41</v>
       </c>
       <c r="K23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>781.03</v>
       </c>
       <c r="L23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>781.49</v>
       </c>
       <c r="M23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>781.6900000000001</v>
       </c>
       <c r="N23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>781.89</v>
       </c>
       <c r="O23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>782.09</v>
       </c>
       <c r="P23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>782.29</v>
       </c>
       <c r="Q23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>782.4400000000001</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>0.8200000000000001</v>
+        <v>782.59</v>
       </c>
       <c r="S23" s="26" t="n">
-        <v>0.01</v>
+        <v>66.94</v>
       </c>
       <c r="T23" s="25" t="inlineStr">
         <is>
@@ -2014,7 +2000,7 @@
     <row r="24">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>Действующие потребители</t>
+          <t>Прочие потребители</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr"/>
@@ -2022,46 +2008,46 @@
       <c r="D24" s="25" t="inlineStr"/>
       <c r="E24" s="25" t="inlineStr"/>
       <c r="F24" s="26" t="n">
-        <v>747.16</v>
+        <v>32.32</v>
       </c>
       <c r="G24" s="26" t="n">
-        <v>748.17</v>
+        <v>14.41</v>
       </c>
       <c r="H24" s="26" t="n">
-        <v>774.15</v>
+        <v>17.52</v>
       </c>
       <c r="I24" s="26" t="n">
-        <v>787.84</v>
+        <v>17.52</v>
       </c>
       <c r="J24" s="26" t="n">
-        <v>790.61</v>
+        <v>20.02</v>
       </c>
       <c r="K24" s="26" t="n">
-        <v>800.38</v>
+        <v>20.17</v>
       </c>
       <c r="L24" s="26" t="n">
-        <v>800.84</v>
+        <v>20.17</v>
       </c>
       <c r="M24" s="26" t="n">
-        <v>801.04</v>
+        <v>20.17</v>
       </c>
       <c r="N24" s="26" t="n">
-        <v>801.24</v>
+        <v>20.17</v>
       </c>
       <c r="O24" s="26" t="n">
-        <v>801.4400000000001</v>
+        <v>20.17</v>
       </c>
       <c r="P24" s="26" t="n">
-        <v>801.64</v>
+        <v>20.17</v>
       </c>
       <c r="Q24" s="26" t="n">
-        <v>801.79</v>
+        <v>20.17</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>801.9400000000001</v>
+        <v>20.17</v>
       </c>
       <c r="S24" s="26" t="n">
-        <v>54.78</v>
+        <v>-12.15</v>
       </c>
       <c r="T24" s="25" t="inlineStr">
         <is>
@@ -2092,34 +2078,34 @@
         <v>27.84</v>
       </c>
       <c r="J25" s="23" t="n">
-        <v>143.6</v>
+        <v>229.2</v>
       </c>
       <c r="K25" s="23" t="n">
-        <v>273.39</v>
+        <v>358.99</v>
       </c>
       <c r="L25" s="23" t="n">
-        <v>377.79</v>
+        <v>548.99</v>
       </c>
       <c r="M25" s="23" t="n">
-        <v>377.79</v>
+        <v>548.99</v>
       </c>
       <c r="N25" s="23" t="n">
-        <v>377.79</v>
+        <v>548.99</v>
       </c>
       <c r="O25" s="23" t="n">
-        <v>375.59</v>
+        <v>546.79</v>
       </c>
       <c r="P25" s="23" t="n">
-        <v>372.99</v>
+        <v>544.1900000000001</v>
       </c>
       <c r="Q25" s="23" t="n">
-        <v>371.09</v>
+        <v>542.29</v>
       </c>
       <c r="R25" s="23" t="n">
-        <v>369.39</v>
+        <v>540.59</v>
       </c>
       <c r="S25" s="23" t="n">
-        <v>369.39</v>
+        <v>540.59</v>
       </c>
       <c r="T25" s="22" t="inlineStr">
         <is>
@@ -2418,68 +2404,68 @@
     <row r="30">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>АО "Каспийский трубопроводный консорциум - Р"(НПС-4А)</t>
+          <t>ГТУ ТЭЦ (объект инфраструктурного инвестора)</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>Нефтяная</t>
+          <t>Электроэнергетика</t>
         </is>
       </c>
       <c r="C30" s="25" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D30" s="25" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E30" s="25" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F30" s="26" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="H30" s="26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="I30" s="26" t="n">
-        <v>12.59</v>
+        <v>0</v>
       </c>
       <c r="J30" s="26" t="n">
-        <v>12.59</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K30" s="26" t="n">
-        <v>14</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="L30" s="26" t="n">
-        <v>14</v>
+        <v>171.2</v>
       </c>
       <c r="M30" s="26" t="n">
-        <v>14</v>
+        <v>171.2</v>
       </c>
       <c r="N30" s="26" t="n">
-        <v>14</v>
+        <v>171.2</v>
       </c>
       <c r="O30" s="26" t="n">
-        <v>11.8</v>
+        <v>171.2</v>
       </c>
       <c r="P30" s="26" t="n">
-        <v>9.199999999999999</v>
+        <v>171.2</v>
       </c>
       <c r="Q30" s="26" t="n">
-        <v>7.3</v>
+        <v>171.2</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>5.6</v>
+        <v>171.2</v>
       </c>
       <c r="S30" s="26" t="n">
-        <v>5.6</v>
+        <v>171.2</v>
       </c>
       <c r="T30" s="25" t="inlineStr">
         <is>
@@ -2501,43 +2487,43 @@
         <v>0</v>
       </c>
       <c r="G31" s="26" t="n">
-        <v>0.32</v>
+        <v>2</v>
       </c>
       <c r="H31" s="26" t="n">
-        <v>6</v>
+        <v>7.68</v>
       </c>
       <c r="I31" s="26" t="n">
-        <v>15.25</v>
+        <v>27.84</v>
       </c>
       <c r="J31" s="26" t="n">
-        <v>24.61</v>
+        <v>37.2</v>
       </c>
       <c r="K31" s="26" t="n">
-        <v>52.59</v>
+        <v>66.59</v>
       </c>
       <c r="L31" s="26" t="n">
-        <v>62.39</v>
+        <v>76.39</v>
       </c>
       <c r="M31" s="26" t="n">
-        <v>62.39</v>
+        <v>76.39</v>
       </c>
       <c r="N31" s="26" t="n">
-        <v>62.39</v>
+        <v>76.39</v>
       </c>
       <c r="O31" s="26" t="n">
-        <v>62.39</v>
+        <v>74.19</v>
       </c>
       <c r="P31" s="26" t="n">
-        <v>62.39</v>
+        <v>71.59</v>
       </c>
       <c r="Q31" s="26" t="n">
-        <v>62.39</v>
+        <v>69.69</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>62.39</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="S31" s="26" t="n">
-        <v>62.39</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="T31" s="25" t="inlineStr">
         <is>
